--- a/docs/posupos-sales/hearing-sheet-1store.xlsx
+++ b/docs/posupos-sales/hearing-sheet-1store.xlsx
@@ -21,12 +21,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="107">
   <si>
     <t xml:space="preserve">ポスポス 導入店の聞き取りシート</t>
   </si>
   <si>
     <t xml:space="preserve">黄色のセルに書き込みます。灰色のセルは自動で計算します。数字は実際に測ったものだけを書き、わからないところは空けておきます（広告に使うのは測った数字だけ）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月額（円・税込）</t>
   </si>
   <si>
     <r>
@@ -828,13 +831,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="165" formatCode="\¥#,##0"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -874,6 +878,20 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF13234A"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF13234A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -888,20 +906,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF13234A"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF13234A"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF13234A"/>
       <name val="WenQuanYi Zen Hei"/>
@@ -925,12 +929,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1557D6"/>
-        <bgColor rgb="FF3366FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE8EEF9"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
@@ -939,6 +937,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6C9"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1557D6"/>
+        <bgColor rgb="FF3366FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -997,7 +1001,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1014,11 +1018,71 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1027,66 +1091,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1375,684 +1383,695 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="A9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="A15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="A19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
+      <c r="A20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
+      <c r="A21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="A23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7" t="s">
+      <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="C24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="D24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="F24" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="G24" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="11" t="str">
+      <c r="B25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12" t="str">
         <f aca="false">IF(OR(C25="",D25=""),"",C25-D25)</f>
         <v/>
       </c>
-      <c r="F25" s="12" t="str">
+      <c r="F25" s="13" t="str">
         <f aca="false">IF(OR(C25="",D25="",N(C25)=0),"",(C25-D25)/C25)</f>
         <v/>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14" t="str">
+      <c r="B26" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15" t="str">
         <f aca="false">IF(OR(C26="",D26=""),"",C26-D26)</f>
         <v/>
       </c>
-      <c r="F26" s="12" t="str">
+      <c r="F26" s="13" t="str">
         <f aca="false">IF(OR(C26="",D26="",N(C26)=0),"",(C26-D26)/C26)</f>
         <v/>
       </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14" t="str">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="15" t="str">
         <f aca="false">IF(OR(C27="",D27=""),"",C27-D27)</f>
         <v/>
       </c>
-      <c r="F27" s="12" t="str">
+      <c r="F27" s="13" t="str">
         <f aca="false">IF(OR(C27="",D27="",N(C27)=0),"",(C27-D27)/C27)</f>
         <v/>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11" t="str">
+      <c r="B28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12" t="str">
         <f aca="false">IF(OR(C28="",D28=""),"",C28-D28)</f>
         <v/>
       </c>
-      <c r="F28" s="12" t="str">
+      <c r="F28" s="13" t="str">
         <f aca="false">IF(OR(C28="",D28="",N(C28)=0),"",(C28-D28)/C28)</f>
         <v/>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11" t="str">
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12" t="str">
         <f aca="false">IF(OR(C29="",D29=""),"",C29-D29)</f>
         <v/>
       </c>
-      <c r="F29" s="12" t="str">
+      <c r="F29" s="13" t="str">
         <f aca="false">IF(OR(C29="",D29="",N(C29)=0),"",(C29-D29)/C29)</f>
         <v/>
       </c>
-      <c r="G29" s="6"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="9" t="s">
+      <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="11" t="str">
+      <c r="B30" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12" t="str">
         <f aca="false">IF(OR(C30="",D30=""),"",C30-D30)</f>
         <v/>
       </c>
-      <c r="F30" s="12" t="str">
+      <c r="F30" s="13" t="str">
         <f aca="false">IF(OR(C30="",D30="",N(C30)=0),"",(C30-D30)/C30)</f>
         <v/>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11" t="str">
+      <c r="B31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="12" t="str">
         <f aca="false">IF(OR(C31="",D31=""),"",C31-D31)</f>
         <v/>
       </c>
-      <c r="F31" s="12" t="str">
+      <c r="F31" s="13" t="str">
         <f aca="false">IF(OR(C31="",D31="",N(C31)=0),"",(C31-D31)/C31)</f>
         <v/>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="11" t="str">
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12" t="str">
         <f aca="false">IF(OR(C32="",D32=""),"",C32-D32)</f>
         <v/>
       </c>
-      <c r="F32" s="12" t="str">
+      <c r="F32" s="13" t="str">
         <f aca="false">IF(OR(C32="",D32="",N(C32)=0),"",(C32-D32)/C32)</f>
         <v/>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11" t="str">
+      <c r="B33" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12" t="str">
         <f aca="false">IF(OR(C33="",D33=""),"",C33-D33)</f>
         <v/>
       </c>
-      <c r="F33" s="12" t="str">
+      <c r="F33" s="13" t="str">
         <f aca="false">IF(OR(C33="",D33="",N(C33)=0),"",(C33-D33)/C33)</f>
         <v/>
       </c>
-      <c r="G33" s="6"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="A34" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="6"/>
+      <c r="B34" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="6"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="6"/>
+      <c r="A36" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+      <c r="A37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="A39" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="7" t="s">
+      <c r="A40" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7" t="s">
+      <c r="B40" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
+      <c r="A41" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="A42" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+      <c r="A43" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+      <c r="A44" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
+      <c r="A45" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+      <c r="A46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
+      <c r="A47" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
+      <c r="A48" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
+      <c r="A49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
+      <c r="A50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
+      <c r="A51" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
+      <c r="A52" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
+      <c r="A53" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
+      <c r="A54" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="A56" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="19" t="str">
+      <c r="A57" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20" t="str">
         <f aca="false">IF(C57="","",IF(C57&gt;=9,"→ このまま紹介をお願いする",IF(C57&gt;=7,"→ 困りごとを聞いてから、紹介をお願いする","→ 紹介はお願いせず、困りごとを先に直す")))</f>
         <v/>
       </c>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
+      <c r="A58" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
+      <c r="A59" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2062,127 +2081,129 @@
       <c r="G61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7" t="s">
+      <c r="A62" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7" t="s">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7" t="s">
+      <c r="D62" s="3"/>
+      <c r="E62" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="5"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="5"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="5"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
+      <c r="A67" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+      <c r="A69" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="21" t="s">
+      <c r="A70" s="9" t="s">
         <v>77</v>
       </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="22" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="21" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="21" t="s">
-        <v>77</v>
+      <c r="A72" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="21" t="s">
-        <v>77</v>
+      <c r="A73" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="97">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:G5"/>
@@ -2347,752 +2368,765 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="n">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="n">
         <v>46331</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="A6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
+      <c r="A7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5" t="n">
+      <c r="A9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="n">
         <v>46235</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-    </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="12" t="n">
         <f aca="false">IF(OR(C25="",D25=""),"",C25-D25)</f>
         <v>30</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <f aca="false">IF(OR(C25="",D25="",N(C25)=0),"",(C25-D25)/C25)</f>
         <v>0.75</v>
       </c>
-      <c r="G25" s="22" t="s">
-        <v>91</v>
+      <c r="G25" s="23" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="B26" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="15" t="n">
         <f aca="false">IF(OR(C26="",D26=""),"",C26-D26)</f>
         <v>8</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="13" t="n">
         <f aca="false">IF(OR(C26="",D26="",N(C26)=0),"",(C26-D26)/C26)</f>
         <v>0.8</v>
       </c>
-      <c r="G26" s="22" t="s">
-        <v>92</v>
+      <c r="G26" s="23" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14" t="str">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="15" t="str">
         <f aca="false">IF(OR(C27="",D27=""),"",C27-D27)</f>
         <v/>
       </c>
-      <c r="F27" s="12" t="str">
+      <c r="F27" s="13" t="str">
         <f aca="false">IF(OR(C27="",D27="",N(C27)=0),"",(C27-D27)/C27)</f>
         <v/>
       </c>
-      <c r="G27" s="22"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="B28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <f aca="false">IF(OR(C28="",D28=""),"",C28-D28)</f>
         <v>12</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="13" t="n">
         <f aca="false">IF(OR(C28="",D28="",N(C28)=0),"",(C28-D28)/C28)</f>
         <v>0.8</v>
       </c>
-      <c r="G28" s="22"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11" t="str">
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12" t="str">
         <f aca="false">IF(OR(C29="",D29=""),"",C29-D29)</f>
         <v/>
       </c>
-      <c r="F29" s="12" t="str">
+      <c r="F29" s="13" t="str">
         <f aca="false">IF(OR(C29="",D29="",N(C29)=0),"",(C29-D29)/C29)</f>
         <v/>
       </c>
-      <c r="G29" s="22"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="9" t="s">
+      <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="11" t="str">
+      <c r="B30" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12" t="str">
         <f aca="false">IF(OR(C30="",D30=""),"",C30-D30)</f>
         <v/>
       </c>
-      <c r="F30" s="12" t="str">
+      <c r="F30" s="13" t="str">
         <f aca="false">IF(OR(C30="",D30="",N(C30)=0),"",(C30-D30)/C30)</f>
         <v/>
       </c>
-      <c r="G30" s="22"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11" t="str">
+      <c r="B31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="12" t="str">
         <f aca="false">IF(OR(C31="",D31=""),"",C31-D31)</f>
         <v/>
       </c>
-      <c r="F31" s="12" t="str">
+      <c r="F31" s="13" t="str">
         <f aca="false">IF(OR(C31="",D31="",N(C31)=0),"",(C31-D31)/C31)</f>
         <v/>
       </c>
-      <c r="G31" s="22"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="11" t="str">
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12" t="str">
         <f aca="false">IF(OR(C32="",D32=""),"",C32-D32)</f>
         <v/>
       </c>
-      <c r="F32" s="12" t="str">
+      <c r="F32" s="13" t="str">
         <f aca="false">IF(OR(C32="",D32="",N(C32)=0),"",(C32-D32)/C32)</f>
         <v/>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11" t="str">
+      <c r="B33" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12" t="str">
         <f aca="false">IF(OR(C33="",D33=""),"",C33-D33)</f>
         <v/>
       </c>
-      <c r="F33" s="12" t="str">
+      <c r="F33" s="13" t="str">
         <f aca="false">IF(OR(C33="",D33="",N(C33)=0),"",(C33-D33)/C33)</f>
         <v/>
       </c>
-      <c r="G33" s="22"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="A34" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="B34" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="22" t="s">
-        <v>93</v>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="23" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="10" t="n">
+      <c r="D35" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="22"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="10" t="n">
+      <c r="A36" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="22"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
+      <c r="A37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="A39" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="7" t="s">
+      <c r="A40" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7" t="s">
+      <c r="B40" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
+      <c r="A41" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="A42" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+      <c r="A43" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+      <c r="A44" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
+      <c r="A45" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="23"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+      <c r="A46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
+      <c r="A47" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22" t="s">
+      <c r="A48" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
+      <c r="A49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="23"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
+      <c r="A50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
+      <c r="A51" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
+      <c r="A52" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
     </row>
     <row r="53" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
+      <c r="A53" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
+      <c r="A54" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="A56" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="18" t="n">
+      <c r="A57" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="D57" s="19" t="str">
+      <c r="D57" s="20" t="str">
         <f aca="false">IF(C57="","",IF(C57&gt;=9,"→ このまま紹介をお願いする",IF(C57&gt;=7,"→ 困りごとを聞いてから、紹介をお願いする","→ 紹介はお願いせず、困りごとを先に直す")))</f>
         <v>→ このまま紹介をお願いする</v>
       </c>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
+      <c r="A58" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
+      <c r="A59" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
     </row>
     <row r="61" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3102,135 +3136,137 @@
       <c r="G61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7" t="s">
+      <c r="A62" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7" t="s">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7" t="s">
+      <c r="D62" s="3"/>
+      <c r="E62" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22" t="s">
+      <c r="A63" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22" t="s">
+      <c r="B63" s="23"/>
+      <c r="C63" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F63" s="22"/>
-      <c r="G63" s="5"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F63" s="23"/>
+      <c r="G63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="5"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="5"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
+      <c r="A67" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
     </row>
     <row r="69" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+      <c r="A69" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="21" t="s">
+      <c r="A70" s="9" t="s">
         <v>77</v>
       </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="22" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="21" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="21" t="s">
-        <v>77</v>
+      <c r="A72" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="21" t="s">
-        <v>77</v>
+      <c r="A73" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="97">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:G5"/>
